--- a/AAII_Financials/Quarterly/RF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>RF</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1839000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1782000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1806000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1811000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1779000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1660000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1695000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1677000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1629000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1595000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1657000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1712000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1839000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1815000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1552000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1343000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1155000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1052000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1056000</v>
-      </c>
-      <c r="V8" s="3">
-        <v>1006000</v>
       </c>
       <c r="W8" s="3">
         <v>1006000</v>
       </c>
       <c r="X8" s="3">
+        <v>1006000</v>
+      </c>
+      <c r="Y8" s="3">
         <v>1013000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1061000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1059000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1063000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1079000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1108000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1150000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1177000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1171000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1158000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1112000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1076000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1047000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1020000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1012000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>989000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>966000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>957000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>942000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1839000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1782000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1806000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1811000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1779000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1660000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1695000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1677000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1629000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1595000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1657000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1712000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1839000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1815000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,52 +1467,55 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-5000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1000</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>1000</v>
       </c>
       <c r="M14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N14" s="3">
         <v>-3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1000</v>
       </c>
       <c r="P14" s="3">
         <v>1000</v>
       </c>
       <c r="Q14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E15" s="3">
         <v>23000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>22000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>21000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>34000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>48000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>59000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>61000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>63000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1635,8 +1657,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
@@ -1653,50 +1675,53 @@
       <c r="AB15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC15" s="3">
-        <v>-10000</v>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD15" s="3">
         <v>-10000</v>
       </c>
       <c r="AE15" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>-12000</v>
       </c>
       <c r="AG15" s="3">
         <v>-12000</v>
       </c>
       <c r="AH15" s="3">
-        <v>-14000</v>
+        <v>-12000</v>
       </c>
       <c r="AI15" s="3">
         <v>-14000</v>
       </c>
       <c r="AJ15" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AK15" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-17000</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>-18000</v>
       </c>
       <c r="AM15" s="3">
         <v>-18000</v>
       </c>
       <c r="AN15" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="AO15" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AO15" s="3">
-        <v>-25000</v>
       </c>
       <c r="AP15" s="3">
         <v>-25000</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>-25000</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1116000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1068000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1098000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1108000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1073000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1039000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1037000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1069000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1003000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1130000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1189000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1089000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1110000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1025000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>263000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>216000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>107000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>147000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-114000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-294000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-96000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>17000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>184000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>973000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>524000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>276000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>321000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>327000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>314000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>283000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>240000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>196000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>112000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>58000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>173000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>137000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>155000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>127000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>723000</v>
+      </c>
+      <c r="E18" s="3">
         <v>714000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>708000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>703000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>706000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>621000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>658000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>608000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>626000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>465000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>468000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>623000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>729000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>790000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1289000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1127000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1048000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1051000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>909000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1120000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1300000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1109000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1044000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>875000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>90000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>555000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>832000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>829000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>850000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>857000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>875000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>872000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>880000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>935000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>962000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>839000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>852000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>811000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>830000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>831000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-417000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-565000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-308000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-349000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-368000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-289000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-279000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-287000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-307000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-241000</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-351000</v>
       </c>
       <c r="AB20" s="3">
         <v>-351000</v>
       </c>
       <c r="AC20" s="3">
+        <v>-351000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-345000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-313000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-367000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-358000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-384000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-417000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-413000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-393000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-421000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-389000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-403000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-391000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-402000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-360000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E21" s="3">
         <v>737000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>730000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>724000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>725000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>643000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>679000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>642000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>667000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>513000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>521000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>682000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>790000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>853000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>941000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>645000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>836000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>807000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>619000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>929000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1115000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>923000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>798000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>766000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-133000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>304000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>592000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>625000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>590000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>604000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>598000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>571000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>585000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>663000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>668000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>586000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>583000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>560000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>577000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>629000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>718000</v>
+      </c>
+      <c r="E23" s="3">
         <v>714000</v>
-      </c>
-      <c r="E23" s="3">
-        <v>708000</v>
       </c>
       <c r="F23" s="3">
         <v>708000</v>
       </c>
       <c r="G23" s="3">
+        <v>708000</v>
+      </c>
+      <c r="H23" s="3">
         <v>706000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>621000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>657000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>608000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>625000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>464000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>471000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>619000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>728000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>789000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>872000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>562000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>740000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>702000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>541000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>831000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1021000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>822000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>737000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>634000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-261000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>204000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>487000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>516000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>483000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>499000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>491000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>455000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>467000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>542000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>541000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>450000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>449000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>420000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>428000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>471000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E24" s="3">
         <v>155000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>174000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>139000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>143000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>131000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>123000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>118000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>124000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>96000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>80000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>129000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>147000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>177000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>187000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>133000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>157000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>154000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>103000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>180000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>231000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>180000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>121000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>104000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-47000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>42000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>98000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>107000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>93000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>105000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>122000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>85000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>89000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>128000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>160000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>138000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>133000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>127000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>134000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E26" s="3">
         <v>559000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>534000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>569000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>563000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>490000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>534000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>490000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>501000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>368000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>391000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>490000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>581000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>612000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>685000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>429000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>583000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>548000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>438000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>651000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>790000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>642000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>616000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>530000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-214000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>162000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>389000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>409000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>390000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>394000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>369000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>370000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>378000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>414000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>381000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>312000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>316000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>293000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>294000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>319000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>549000</v>
+      </c>
+      <c r="E27" s="3">
         <v>539000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>514000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>548000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>534000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>465000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>508000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>446000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>477000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>343000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>367000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>465000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>556000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>588000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>660000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>404000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>558000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>524000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>414000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>624000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>748000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>614000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>588000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>501000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>139000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>366000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>385000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>374000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>378000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>353000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>354000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>362000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>398000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>365000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>296000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>300000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>277000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>278000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>303000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3196,14 +3256,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3215,37 +3275,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>37000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>194000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-46000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>8000</v>
-      </c>
-      <c r="AO29" s="3">
-        <v>1000</v>
       </c>
       <c r="AP29" s="3">
         <v>1000</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>417000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>565000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>308000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>349000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>368000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>289000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>279000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>287000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>307000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>241000</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>351000</v>
       </c>
       <c r="AB32" s="3">
         <v>351000</v>
       </c>
       <c r="AC32" s="3">
+        <v>351000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>345000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>313000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>367000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>358000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>384000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>417000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>413000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>393000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>421000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>389000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>403000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>391000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>402000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>360000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E33" s="3">
         <v>559000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>534000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>569000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>563000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>490000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>534000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>490000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>501000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>368000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>391000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>490000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>581000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>612000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>660000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>404000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>558000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>524000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>414000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>624000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>748000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>614000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>588000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>501000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>139000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>366000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>385000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>374000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>378000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>390000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>548000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>398000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>319000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>295000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>300000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>285000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>279000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>304000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E35" s="3">
         <v>559000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>534000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>569000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>563000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>490000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>534000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>490000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>501000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>368000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>391000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>490000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>581000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>612000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>660000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>404000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>558000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>524000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>414000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>624000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>748000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>614000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>588000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>501000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>139000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>366000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>385000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>374000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>378000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>390000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>548000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>398000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>319000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>295000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>300000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>285000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>279000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>304000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,252 +4276,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3526000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3643000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3307000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3073000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3245000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3287000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10712000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2665000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2955000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2527000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2635000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1554000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2480000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2395000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1997000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2117000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2301000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2227000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1350000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1741000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1820000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1918000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1558000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1972000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1619000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2101000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1598000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1966000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2026000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1666000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2018000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1911000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1844000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1766000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2012000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1829000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1873000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1736000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1853000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1928000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1476000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1570000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1335000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1408000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1496000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1548000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1816000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1640000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2093000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2231000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2105000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2979000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3424000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2346000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>9230000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>13549000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18199000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>25718000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>28061000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>25766000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>23774000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>23002000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>16398000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>11501000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11579000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5071000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2516000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3101000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2141000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1520000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1584000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2442000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1419000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>2158000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2125000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2436000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>2764000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>3722000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>2430000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,40 +4649,43 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E44" s="3">
         <v>20000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>15000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>15000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
-      </c>
-      <c r="M44" s="3">
-        <v>15000</v>
       </c>
       <c r="N44" s="3">
         <v>15000</v>
@@ -4602,7 +4697,7 @@
         <v>15000</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E45" s="3">
         <v>569000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>571000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>574000</v>
       </c>
       <c r="G45" s="3">
         <v>574000</v>
       </c>
       <c r="H45" s="3">
+        <v>574000</v>
+      </c>
+      <c r="I45" s="3">
         <v>583000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>572000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>596000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>608000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>588000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>614000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>625000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>575000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>538000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12507000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13766000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13341000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14672000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13855000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16807000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13708000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13296000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11747000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14499000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9935000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13094000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14454000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12296000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35190000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35389000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>36041000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>34827000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>34747000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33349000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>33279000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>33784000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31849000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>30824000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>31366000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27736000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28808000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29670000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1704000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1666000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2123000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1742000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1755000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1726000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2126000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1648000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1630000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1635000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2104000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1616000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1622000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1705000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1718000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1744000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1768000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1794000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1814000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1805000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1825000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1852000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1897000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1896000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1929000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1935000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2403000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2393000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2380000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2456000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2045000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2051000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2050000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2065000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2064000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2057000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2060000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2088000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2096000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2075000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6817000</v>
+      </c>
+      <c r="E49" s="3">
         <v>6820000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6843000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6855000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6874000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6873000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6909000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6882000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6940000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6955000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6844000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6881000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6760000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6761000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6794000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6814000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6798000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6582000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6467000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5692000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5681000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5696000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5608000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5583000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5579000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5197000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5295000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5263000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5267000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5323000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5362000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5357000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5422000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5427000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5417000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5426000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5448000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5439000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5449000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5348000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,53 +5649,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7370000</v>
+      </c>
+      <c r="E52" s="3">
         <v>6701000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6385000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>6864000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6971000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6166000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6634000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5999000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5751000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5142000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6902000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6334000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7118000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>161299000</v>
+      </c>
+      <c r="E54" s="3">
         <v>160741000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>158814000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>159940000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>159206000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>159846000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>157302000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>157426000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>154052000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>154909000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>152194000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>153624000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>155656000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>154135000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>155220000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>157798000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>160908000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>164082000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>162938000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>156153000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>155610000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>153331000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>147389000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>145180000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>144070000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>133542000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>126240000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>128147000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>127518000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>128802000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>125688000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>124578000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>124557000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>122913000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>124294000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>123271000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>124643000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>124545000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>125968000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>125177000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>130710000</v>
+      </c>
+      <c r="E57" s="3">
         <v>131880000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>131128000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>130334000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>130919000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>130971000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>127603000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>126376000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>126616000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>128982000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>127788000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>126199000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>126959000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>128460000</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4857000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4969000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2286000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2947000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1833000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2858000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3951000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4057000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4298000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4096000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2791000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6226000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7358000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4852000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,8 +6411,8 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -6308,24 +6444,24 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>514000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>523000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>505000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>511000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6335,8 +6471,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>135567000</v>
+      </c>
+      <c r="E60" s="3">
         <v>136849000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>133414000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>133281000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>132752000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>133829000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>131554000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>130433000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>130914000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>133078000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>130579000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>132425000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134317000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>133312000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4628000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3137000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4582000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4635000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5128000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5118000</v>
       </c>
-      <c r="I61" s="3">
-        <v>5093000</v>
-      </c>
       <c r="J61" s="3">
+        <v>5620000</v>
+      </c>
+      <c r="K61" s="3">
         <v>5267000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4234000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3327000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2765000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4290000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4293000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2307000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2284000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2274000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2319000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2343000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2407000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2451000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2870000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2916000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3569000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4919000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6007000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5454000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5378000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6127000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6111000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>6055000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>5522000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5475000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4737000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5346000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4479000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4499000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3511000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3506000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3509000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3550000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2193000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1911000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1647000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2929000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2620000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2332000</v>
       </c>
-      <c r="I62" s="3">
-        <v>2671000</v>
-      </c>
       <c r="J62" s="3">
+        <v>2144000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2999000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1702000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1426000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1275000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>784000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>385000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1614000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>142388000</v>
+      </c>
+      <c r="E66" s="3">
         <v>141897000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>139711000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>140845000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>140500000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>141279000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>139392000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>138699000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>136850000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137831000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>134701000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>137499000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>138995000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>137233000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>139273000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>142625000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>144401000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>147100000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>144612000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>137548000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>137358000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>135469000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>129278000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>127276000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>126468000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>116210000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>109945000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>111566000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>110910000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>113290000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>110598000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>109808000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>108780000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>107047000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>108102000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>106647000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>107750000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>107823000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>109304000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>107812000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7513,7 +7680,7 @@
         <v>1369000</v>
       </c>
       <c r="H70" s="3">
-        <v>1715000</v>
+        <v>1369000</v>
       </c>
       <c r="I70" s="3">
         <v>1715000</v>
@@ -7522,7 +7689,7 @@
         <v>1715000</v>
       </c>
       <c r="K70" s="3">
-        <v>1659000</v>
+        <v>1715000</v>
       </c>
       <c r="L70" s="3">
         <v>1659000</v>
@@ -7561,7 +7728,7 @@
         <v>1659000</v>
       </c>
       <c r="X70" s="3">
-        <v>1656000</v>
+        <v>1659000</v>
       </c>
       <c r="Y70" s="3">
         <v>1656000</v>
@@ -7573,7 +7740,7 @@
         <v>1656000</v>
       </c>
       <c r="AB70" s="3">
-        <v>1310000</v>
+        <v>1656000</v>
       </c>
       <c r="AC70" s="3">
         <v>1310000</v>
@@ -7585,7 +7752,7 @@
         <v>1310000</v>
       </c>
       <c r="AF70" s="3">
-        <v>820000</v>
+        <v>1310000</v>
       </c>
       <c r="AG70" s="3">
         <v>820000</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>820000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>820000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10840000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10517000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10205000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9922000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9609000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9299000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9060000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8778000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8561000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8304000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8186000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8042000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7802000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7433000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7004000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6531000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6314000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5915000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5550000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5296000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4836000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4235000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3770000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3330000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2978000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3364000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3751000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3534000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3299000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3066000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2828000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2582000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2182000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1923000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1628000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1279000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1089000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>873000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>666000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>465000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17471000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17410000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17674000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17680000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17297000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16815000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16164000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16961000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15510000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15385000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15770000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14441000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14980000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15224000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14288000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13514000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14848000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15323000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16667000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16946000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16593000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16206000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16455000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16248000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15946000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16022000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14985000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15271000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15298000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14692000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14270000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13950000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14957000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>15046000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15372000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15804000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>16073000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>15902000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>15844000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>16545000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>570000</v>
+      </c>
+      <c r="E81" s="3">
         <v>559000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>534000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>569000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>563000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>490000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>534000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>490000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>501000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>368000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>391000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>490000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>581000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>612000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>660000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>404000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>558000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>524000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>414000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>624000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>748000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>614000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>588000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>501000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-237000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>139000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>366000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>385000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>374000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>378000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>390000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>548000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>359000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>398000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>319000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>295000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>300000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>285000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>279000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>304000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E83" s="3">
         <v>22000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>41000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>53000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>59000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>61000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>83000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>96000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>105000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>69000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>83000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>96000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>105000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>78000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>98000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>94000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>101000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>61000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>132000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>128000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>100000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>105000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>109000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>107000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>105000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>107000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>116000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>118000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>121000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>127000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>136000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>134000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>140000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>149000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>158000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E89" s="3">
         <v>867000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-319000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>861000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>573000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1066000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-220000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1261000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>161000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>396000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>855000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>860000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>397000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>196000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1276000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>321000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>921000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>584000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>761000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>841000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>709000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>719000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>681000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>857000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>787000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>497000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>763000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>743000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>578000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1004000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>611000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>506000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>154000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>293000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>849000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>419000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>736000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>214000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>610000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,86 +9926,89 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-54000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-49000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-174000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-101000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-51000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-45000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-51000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-72000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-19000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-55000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-69000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-32000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-42000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-254000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-154000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1380000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2180000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>218000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>346000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2148000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>166000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>498000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-498000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1471000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1209000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-156000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>243000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-598000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1096000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1869000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2085000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5388000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3599000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2513000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1127000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1412000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1977000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-414000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1136000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5280000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>287000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>187000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1723000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1688000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1211000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1120000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-670000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-44000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-823000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>596000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-433000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-125000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-128000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>573000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,43 +10426,44 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E96" s="3">
         <v>230000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>235000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>224000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>226000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>227000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>228000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>220000</v>
       </c>
       <c r="K96" s="3">
         <v>220000</v>
       </c>
       <c r="L96" s="3">
+        <v>220000</v>
+      </c>
+      <c r="M96" s="3">
         <v>222000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>226000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>187000</v>
       </c>
       <c r="O96" s="3">
         <v>187000</v>
@@ -10239,25 +10472,25 @@
         <v>187000</v>
       </c>
       <c r="Q96" s="3">
+        <v>187000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-185000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-159000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-158000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-161000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-162000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-148000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-149000</v>
       </c>
       <c r="X96" s="3">
         <v>-149000</v>
@@ -10266,58 +10499,61 @@
         <v>-149000</v>
       </c>
       <c r="Z96" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-148000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-149000</v>
       </c>
       <c r="AB96" s="3">
         <v>-149000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-140000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-143000</v>
       </c>
       <c r="AF96" s="3">
         <v>-143000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-148000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-101000</v>
       </c>
       <c r="AI96" s="3">
         <v>-101000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-102000</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-105000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-84000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-157000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-81000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-82000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1549000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1091000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-283000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1566000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2372000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-87000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1279000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1461000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2844000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2914000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1973000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1254000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1494000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3846000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3070000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2978000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1549000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3656000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-55000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1377000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6312000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2507000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8222000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5634000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1737000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-371000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1785000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1379000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>250000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-282000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1265000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-906000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>729000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1781000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-230000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1684000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1127000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1182000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1217000</v>
+      </c>
+      <c r="E102" s="3">
         <v>236000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1192000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>924000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3141000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3604000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>191000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2042000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2771000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4449000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2215000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-870000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1053000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2394000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4439000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4834000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7445000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1466000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1904000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1913000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>674000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6964000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4483000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>275000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7943000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1141000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-953000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>579000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>681000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>269000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>43000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-791000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1101000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-796000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>220000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-370000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-243000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1077000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1213000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1000</v>
       </c>
     </row>
